--- a/sheets/대금율보/검수/애.xlsx
+++ b/sheets/대금율보/검수/애.xlsx
@@ -4524,7 +4524,7 @@
       <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">浹汰
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="24"/>
@@ -4610,11 +4610,7 @@
         </is>
       </c>
       <c r="K5" s="25"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="25"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
@@ -4623,11 +4619,7 @@
         </is>
       </c>
       <c r="O5" s="25"/>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P5" s="21"/>
       <c r="Q5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
@@ -4643,15 +4635,13 @@
       <c r="E6" s="26"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I6" s="26"/>
@@ -4686,8 +4676,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -4711,8 +4700,7 @@
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K7" s="22"/>
@@ -4724,8 +4712,7 @@
       <c r="M7" s="22"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O7" s="22"/>
@@ -4746,7 +4733,7 @@
       <c r="C8" s="25"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
@@ -4771,7 +4758,7 @@
       <c r="K8" s="25"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
@@ -4875,8 +4862,7 @@
       <c r="M10" s="26"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="O10" s="26"/>
@@ -4919,8 +4905,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹
-‹</t>
+          <t xml:space="preserve">浹</t>
         </is>
       </c>
       <c r="C12" s="25"/>
@@ -4932,8 +4917,7 @@
       <c r="I12" s="25"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹
-‹</t>
+          <t xml:space="preserve">浹</t>
         </is>
       </c>
       <c r="K12" s="25"/>
@@ -5085,8 +5069,7 @@
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C16" s="25"/>
@@ -5111,8 +5094,7 @@
       <c r="I16" s="25"/>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K16" s="25"/>
@@ -5145,7 +5127,7 @@
       <c r="C17" s="25"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
@@ -5170,7 +5152,7 @@
       <c r="K17" s="25"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
@@ -5183,7 +5165,7 @@
       <c r="O17" s="27"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
@@ -5205,15 +5187,13 @@
       <c r="E18" s="26"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I18" s="26"/>

--- a/sheets/대금율보/검수/애.xlsx
+++ b/sheets/대금율보/검수/애.xlsx
@@ -4469,28 +4469,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.84" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.84" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="25"/>
@@ -4588,7 +4588,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.84" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.84" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Q6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.84" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.84" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="Q8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.84" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Q9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.84" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.84" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       <c r="P11" s="21"/>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.84" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
       <c r="P12" s="21"/>
       <c r="Q12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.84" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.84" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="Q14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.84" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="Q15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.84" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Q16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.84" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="Q17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.84" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Q18" s="28"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.84" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.84" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="25"/>
@@ -5272,7 +5272,7 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.84" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -5291,7 +5291,7 @@
       <c r="P21" s="21"/>
       <c r="Q21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.84" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -5352,6 +5352,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>